--- a/SWARM-EX/Planning/Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/Personal Waterfall Chart Justin Le.xlsx
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E3" s="22" t="n">
         <f aca="false">SUM(F3:W3)</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F3" s="23" t="n">
         <f aca="false">F4+F7+F11+F14</f>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I3" s="23" t="n">
         <f aca="false">I4+I7+I11+I14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J3" s="23" t="n">
         <f aca="false">J4+J7+J11+J14</f>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E4" s="32" t="n">
         <f aca="false">SUM(F4:W4)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" s="33" t="n">
         <f aca="false">SUM(F5:F6)</f>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="I4" s="33" t="n">
         <f aca="false">SUM(I5:I6)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">SUM(J5:J6)</f>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="E5" s="32" t="n">
         <f aca="false">SUM(F5:W5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="42" t="n">
         <v>1</v>
@@ -2579,7 +2579,9 @@
       <c r="H5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="33"/>
+      <c r="I5" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" s="33"/>
       <c r="K5" s="33"/>
       <c r="L5" s="33"/>
@@ -2619,7 +2621,7 @@
       </c>
       <c r="E6" s="50" t="n">
         <f aca="false">SUM(F6:W6)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" s="51" t="n">
         <v>2</v>
@@ -2630,7 +2632,9 @@
       <c r="H6" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="52"/>
+      <c r="I6" s="52" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
@@ -2669,7 +2673,7 @@
       </c>
       <c r="E7" s="32" t="n">
         <f aca="false">SUM(F7:W7)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" s="56" t="n">
         <f aca="false">SUM(F8:F10)</f>
@@ -2685,7 +2689,7 @@
       </c>
       <c r="I7" s="56" t="n">
         <f aca="false">SUM(I8:I10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="56" t="n">
         <f aca="false">SUM(J8:J10)</f>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="E8" s="32" t="n">
         <f aca="false">SUM(F8:W8)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>1</v>
@@ -2777,7 +2781,9 @@
       <c r="H8" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="33"/>
+      <c r="I8" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" s="33"/>
       <c r="K8" s="33"/>
       <c r="L8" s="33"/>
@@ -2815,7 +2821,7 @@
       </c>
       <c r="E9" s="32" t="n">
         <f aca="false">SUM(F9:W9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>1</v>
@@ -2826,7 +2832,9 @@
       <c r="H9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="33"/>
+      <c r="I9" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J9" s="33"/>
       <c r="K9" s="33"/>
       <c r="L9" s="33"/>
@@ -2860,7 +2868,7 @@
       </c>
       <c r="E10" s="50" t="n">
         <f aca="false">SUM(F10:W10)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="51" t="n">
         <v>2</v>
@@ -2871,7 +2879,9 @@
       <c r="H10" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="52"/>
+      <c r="I10" s="52" t="n">
+        <v>1</v>
+      </c>
       <c r="J10" s="52"/>
       <c r="K10" s="52"/>
       <c r="L10" s="52"/>
@@ -2906,7 +2916,7 @@
       </c>
       <c r="E11" s="32" t="n">
         <f aca="false">SUM(F11:W11)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11" s="56" t="n">
         <f aca="false">SUM(F12:F13)</f>
@@ -2922,7 +2932,7 @@
       </c>
       <c r="I11" s="56" t="n">
         <f aca="false">SUM(I12:I13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="56" t="n">
         <f aca="false">SUM(J12:J13)</f>
@@ -3048,7 +3058,7 @@
       </c>
       <c r="E13" s="50" t="n">
         <f aca="false">SUM(F13:W13)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F13" s="51" t="n">
         <v>4</v>
@@ -3059,7 +3069,9 @@
       <c r="H13" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="52"/>
+      <c r="I13" s="52" t="n">
+        <v>2</v>
+      </c>
       <c r="J13" s="52"/>
       <c r="K13" s="52"/>
       <c r="L13" s="52"/>
@@ -3285,7 +3297,7 @@
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">SUM(F17:W17)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="68" t="n">
         <f aca="false">F18+F21+F23+F26</f>
@@ -3301,7 +3313,7 @@
       </c>
       <c r="I17" s="68" t="n">
         <f aca="false">I18+I21+I23+I26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="68" t="n">
         <f aca="false">J18+J21+J23+J26</f>
@@ -3556,7 +3568,7 @@
       </c>
       <c r="E21" s="32" t="n">
         <f aca="false">SUM(F21:W21)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="56" t="n">
         <f aca="false">SUM(F22)</f>
@@ -3572,7 +3584,7 @@
       </c>
       <c r="I21" s="56" t="n">
         <f aca="false">SUM(I22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="56" t="n">
         <f aca="false">SUM(J22)</f>
@@ -3651,14 +3663,16 @@
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">SUM(F22:W22)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="33"/>
+      <c r="I22" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
@@ -3974,7 +3988,7 @@
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">SUM(F29:W29)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F29" s="68" t="n">
         <f aca="false">F30+F41+F47</f>
@@ -3990,7 +4004,7 @@
       </c>
       <c r="I29" s="68" t="n">
         <f aca="false">I30+I41+I47</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" s="68" t="n">
         <f aca="false">J30+J41+J47</f>
@@ -4063,7 +4077,7 @@
       </c>
       <c r="E30" s="32" t="n">
         <f aca="false">SUM(F30:W30)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="56" t="n">
         <f aca="false">SUM(F31:F40)</f>
@@ -4079,7 +4093,7 @@
       </c>
       <c r="I30" s="34" t="n">
         <f aca="false">SUM(I31:I40)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="34" t="n">
         <f aca="false">SUM(J31:J40)</f>
@@ -4156,14 +4170,16 @@
       </c>
       <c r="E31" s="32" t="n">
         <f aca="false">SUM(F31:W31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="42"/>
       <c r="G31" s="33"/>
       <c r="H31" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="77"/>
+      <c r="I31" s="77" t="n">
+        <v>1</v>
+      </c>
       <c r="J31" s="33"/>
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
@@ -4197,12 +4213,14 @@
       </c>
       <c r="E32" s="32" t="n">
         <f aca="false">SUM(F32:W32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="42"/>
       <c r="G32" s="33"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="77"/>
+      <c r="I32" s="77" t="n">
+        <v>1</v>
+      </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33"/>
       <c r="L32" s="33"/>
@@ -4549,7 +4567,7 @@
       </c>
       <c r="E41" s="32" t="n">
         <f aca="false">SUM(F41:W41)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F41" s="56" t="n">
         <f aca="false">SUM(F42:F46)</f>
@@ -4565,7 +4583,7 @@
       </c>
       <c r="I41" s="34" t="n">
         <f aca="false">SUM(I42:I46)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" s="34" t="n">
         <f aca="false">SUM(J42:J46)</f>
@@ -4642,12 +4660,14 @@
       </c>
       <c r="E42" s="32" t="n">
         <f aca="false">SUM(F42:W42)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" s="42"/>
       <c r="G42" s="33"/>
       <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
+      <c r="I42" s="33" t="n">
+        <v>2</v>
+      </c>
       <c r="J42" s="33"/>
       <c r="K42" s="33"/>
       <c r="L42" s="33"/>
@@ -4681,12 +4701,14 @@
       </c>
       <c r="E43" s="32" t="n">
         <f aca="false">SUM(F43:W43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="33"/>
       <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="I43" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J43" s="33"/>
       <c r="K43" s="33"/>
       <c r="L43" s="33"/>
@@ -5245,7 +5267,7 @@
       </c>
       <c r="E56" s="82" t="n">
         <f aca="false">E29+E17+E3</f>
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F56" s="82" t="n">
         <f aca="false">F29+F17+F3</f>
@@ -5261,7 +5283,7 @@
       </c>
       <c r="I56" s="82" t="n">
         <f aca="false">I29+I17+I3</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J56" s="82" t="n">
         <f aca="false">J29+J17+J3</f>
@@ -5400,7 +5422,7 @@
       </c>
       <c r="E58" s="84" t="n">
         <f aca="false">E57-E56</f>
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F58" s="84" t="n">
         <f aca="false">F57-F56</f>
@@ -5416,7 +5438,7 @@
       </c>
       <c r="I58" s="84" t="n">
         <f aca="false">I57-I56</f>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J58" s="84" t="n">
         <f aca="false">J57-J56</f>

--- a/SWARM-EX/Planning/Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/Personal Waterfall Chart Justin Le.xlsx
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F42" authorId="0">
+    <comment ref="F44" authorId="0">
       <text>
         <r>
           <rPr>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t xml:space="preserve">Total Hours</t>
   </si>
@@ -344,9 +344,15 @@
     <t xml:space="preserve">MCT: Review test docs</t>
   </si>
   <si>
+    <t xml:space="preserve">Late (In Progress)</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCT: Bench setup</t>
   </si>
   <si>
+    <t xml:space="preserve">MCT: Hydra development</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCT: Practice run-through of test</t>
   </si>
   <si>
@@ -360,6 +366,9 @@
   </si>
   <si>
     <t xml:space="preserve">SCT-1: Bench setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCT-1: Hydra development</t>
   </si>
   <si>
     <t xml:space="preserve">SCT-1: Practice run-through of test</t>
@@ -2222,7 +2231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB991"/>
+  <dimension ref="A1:AB993"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
@@ -2367,8 +2376,8 @@
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="20" t="n">
-        <f aca="false">D3/$D$56</f>
-        <v>0.364016736401674</v>
+        <f aca="false">D3/$D$58</f>
+        <v>0.350806451612903</v>
       </c>
       <c r="D3" s="21" t="n">
         <f aca="false">D4+D7+D11+D14</f>
@@ -2376,7 +2385,7 @@
       </c>
       <c r="E3" s="22" t="n">
         <f aca="false">SUM(F3:W3)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F3" s="23" t="n">
         <f aca="false">F4+F7+F11+F14</f>
@@ -2396,7 +2405,7 @@
       </c>
       <c r="J3" s="23" t="n">
         <f aca="false">J4+J7+J11+J14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" s="23" t="n">
         <f aca="false">K4+K7+K11+K14</f>
@@ -2469,7 +2478,7 @@
       </c>
       <c r="E4" s="32" t="n">
         <f aca="false">SUM(F4:W4)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" s="33" t="n">
         <f aca="false">SUM(F5:F6)</f>
@@ -2489,7 +2498,7 @@
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">SUM(J5:J6)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="33" t="n">
         <f aca="false">SUM(K5:K6)</f>
@@ -2568,7 +2577,7 @@
       </c>
       <c r="E5" s="32" t="n">
         <f aca="false">SUM(F5:W5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="42" t="n">
         <v>1</v>
@@ -2582,7 +2591,9 @@
       <c r="I5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="33"/>
+      <c r="J5" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" s="33"/>
       <c r="L5" s="33"/>
       <c r="M5" s="33"/>
@@ -2621,7 +2632,7 @@
       </c>
       <c r="E6" s="50" t="n">
         <f aca="false">SUM(F6:W6)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" s="51" t="n">
         <v>2</v>
@@ -2635,7 +2646,9 @@
       <c r="I6" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="52"/>
+      <c r="J6" s="52" t="n">
+        <v>2</v>
+      </c>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
       <c r="M6" s="52"/>
@@ -2673,7 +2686,7 @@
       </c>
       <c r="E7" s="32" t="n">
         <f aca="false">SUM(F7:W7)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F7" s="56" t="n">
         <f aca="false">SUM(F8:F10)</f>
@@ -2693,7 +2706,7 @@
       </c>
       <c r="J7" s="56" t="n">
         <f aca="false">SUM(J8:J10)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="56" t="n">
         <f aca="false">SUM(K8:K10)</f>
@@ -2770,7 +2783,7 @@
       </c>
       <c r="E8" s="32" t="n">
         <f aca="false">SUM(F8:W8)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>1</v>
@@ -2784,7 +2797,9 @@
       <c r="I8" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="33"/>
+      <c r="J8" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" s="33"/>
       <c r="L8" s="33"/>
       <c r="M8" s="33"/>
@@ -2821,7 +2836,7 @@
       </c>
       <c r="E9" s="32" t="n">
         <f aca="false">SUM(F9:W9)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>1</v>
@@ -2835,7 +2850,9 @@
       <c r="I9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="33"/>
+      <c r="J9" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" s="33"/>
       <c r="L9" s="33"/>
       <c r="M9" s="33"/>
@@ -2868,7 +2885,7 @@
       </c>
       <c r="E10" s="50" t="n">
         <f aca="false">SUM(F10:W10)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" s="51" t="n">
         <v>2</v>
@@ -2882,7 +2899,9 @@
       <c r="I10" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="52"/>
+      <c r="J10" s="52" t="n">
+        <v>3</v>
+      </c>
       <c r="K10" s="52"/>
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
@@ -3288,8 +3307,8 @@
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="20" t="n">
-        <f aca="false">D17/$D$56</f>
-        <v>0.292887029288703</v>
+        <f aca="false">D17/$D$58</f>
+        <v>0.282258064516129</v>
       </c>
       <c r="D17" s="21" t="n">
         <f aca="false">D18+D21+D23+D26</f>
@@ -3297,7 +3316,7 @@
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">SUM(F17:W17)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="68" t="n">
         <f aca="false">F18+F21+F23+F26</f>
@@ -3317,7 +3336,7 @@
       </c>
       <c r="J17" s="68" t="n">
         <f aca="false">J18+J21+J23+J26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="68" t="n">
         <f aca="false">K18+K21+K23+K26</f>
@@ -3568,7 +3587,7 @@
       </c>
       <c r="E21" s="32" t="n">
         <f aca="false">SUM(F21:W21)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="56" t="n">
         <f aca="false">SUM(F22)</f>
@@ -3588,7 +3607,7 @@
       </c>
       <c r="J21" s="56" t="n">
         <f aca="false">SUM(J22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="56" t="n">
         <f aca="false">SUM(K22)</f>
@@ -3663,7 +3682,7 @@
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">SUM(F22:W22)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="33"/>
@@ -3673,7 +3692,9 @@
       <c r="I22" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="33"/>
+      <c r="J22" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
       <c r="M22" s="33"/>
@@ -3979,83 +4000,83 @@
       </c>
       <c r="B29" s="67"/>
       <c r="C29" s="20" t="n">
-        <f aca="false">D29/$D$56</f>
-        <v>0.343096234309623</v>
+        <f aca="false">D29/$D$58</f>
+        <v>0.366935483870968</v>
       </c>
       <c r="D29" s="21" t="n">
-        <f aca="false">D30+D41+D47</f>
-        <v>82</v>
+        <f aca="false">D30+D43+D49</f>
+        <v>91</v>
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">SUM(F29:W29)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F29" s="68" t="n">
-        <f aca="false">F30+F41+F47</f>
+        <f aca="false">F30+F43+F49</f>
         <v>0</v>
       </c>
       <c r="G29" s="68" t="n">
-        <f aca="false">G30+G41+G47</f>
+        <f aca="false">G30+G43+G49</f>
         <v>2</v>
       </c>
       <c r="H29" s="68" t="n">
-        <f aca="false">H30+H41+H47</f>
+        <f aca="false">H30+H43+H49</f>
         <v>3</v>
       </c>
       <c r="I29" s="68" t="n">
-        <f aca="false">I30+I41+I47</f>
+        <f aca="false">I30+I43+I49</f>
         <v>5</v>
       </c>
       <c r="J29" s="68" t="n">
-        <f aca="false">J30+J41+J47</f>
-        <v>0</v>
+        <f aca="false">J30+J43+J49</f>
+        <v>6</v>
       </c>
       <c r="K29" s="68" t="n">
-        <f aca="false">K30+K41+K47</f>
+        <f aca="false">K30+K43+K49</f>
         <v>0</v>
       </c>
       <c r="L29" s="68" t="n">
-        <f aca="false">L30+L41+L47</f>
+        <f aca="false">L30+L43+L49</f>
         <v>0</v>
       </c>
       <c r="M29" s="68" t="n">
-        <f aca="false">M30+M41+M47</f>
+        <f aca="false">M30+M43+M49</f>
         <v>0</v>
       </c>
       <c r="N29" s="68" t="n">
-        <f aca="false">N30+N41+N47</f>
+        <f aca="false">N30+N43+N49</f>
         <v>0</v>
       </c>
       <c r="O29" s="68" t="n">
-        <f aca="false">O30+O41+O47</f>
+        <f aca="false">O30+O43+O49</f>
         <v>0</v>
       </c>
       <c r="P29" s="68" t="n">
-        <f aca="false">P30+P41+P47</f>
+        <f aca="false">P30+P43+P49</f>
         <v>0</v>
       </c>
       <c r="Q29" s="68" t="n">
-        <f aca="false">Q30+Q41+Q47</f>
+        <f aca="false">Q30+Q43+Q49</f>
         <v>0</v>
       </c>
       <c r="R29" s="68" t="n">
-        <f aca="false">R30+R41+R47</f>
+        <f aca="false">R30+R43+R49</f>
         <v>0</v>
       </c>
       <c r="S29" s="68" t="n">
-        <f aca="false">S30+S41+S47</f>
+        <f aca="false">S30+S43+S49</f>
         <v>0</v>
       </c>
       <c r="T29" s="68" t="n">
-        <f aca="false">T30+T41+T47</f>
+        <f aca="false">T30+T43+T49</f>
         <v>0</v>
       </c>
       <c r="U29" s="68" t="n">
-        <f aca="false">U30+U41+U47</f>
+        <f aca="false">U30+U43+U49</f>
         <v>0</v>
       </c>
       <c r="V29" s="68" t="n">
-        <f aca="false">V30+V41+V47</f>
+        <f aca="false">V30+V43+V49</f>
         <v>0</v>
       </c>
       <c r="W29" s="69"/>
@@ -4072,83 +4093,83 @@
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="31" t="n">
-        <f aca="false">SUM(D31:D40)</f>
-        <v>20</v>
+        <f aca="false">SUM(D31:D42)</f>
+        <v>29</v>
       </c>
       <c r="E30" s="32" t="n">
         <f aca="false">SUM(F30:W30)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F30" s="56" t="n">
-        <f aca="false">SUM(F31:F40)</f>
+        <f aca="false">SUM(F31:F42)</f>
         <v>0</v>
       </c>
       <c r="G30" s="34" t="n">
-        <f aca="false">SUM(G31:G40)</f>
+        <f aca="false">SUM(G31:G42)</f>
         <v>0</v>
       </c>
       <c r="H30" s="34" t="n">
-        <f aca="false">SUM(H31:H40)</f>
+        <f aca="false">SUM(H31:H42)</f>
         <v>1</v>
       </c>
       <c r="I30" s="34" t="n">
-        <f aca="false">SUM(I31:I40)</f>
+        <f aca="false">SUM(I31:I42)</f>
         <v>2</v>
       </c>
       <c r="J30" s="34" t="n">
-        <f aca="false">SUM(J31:J40)</f>
-        <v>0</v>
+        <f aca="false">SUM(J31:J42)</f>
+        <v>4</v>
       </c>
       <c r="K30" s="34" t="n">
-        <f aca="false">SUM(K31:K40)</f>
+        <f aca="false">SUM(K31:K42)</f>
         <v>0</v>
       </c>
       <c r="L30" s="34" t="n">
-        <f aca="false">SUM(L31:L40)</f>
+        <f aca="false">SUM(L31:L42)</f>
         <v>0</v>
       </c>
       <c r="M30" s="34" t="n">
-        <f aca="false">SUM(M31:M40)</f>
+        <f aca="false">SUM(M31:M42)</f>
         <v>0</v>
       </c>
       <c r="N30" s="34" t="n">
-        <f aca="false">SUM(N31:N40)</f>
+        <f aca="false">SUM(N31:N42)</f>
         <v>0</v>
       </c>
       <c r="O30" s="34" t="n">
-        <f aca="false">SUM(O31:O40)</f>
+        <f aca="false">SUM(O31:O42)</f>
         <v>0</v>
       </c>
       <c r="P30" s="34" t="n">
-        <f aca="false">SUM(P31:P40)</f>
+        <f aca="false">SUM(P31:P42)</f>
         <v>0</v>
       </c>
       <c r="Q30" s="34" t="n">
-        <f aca="false">SUM(Q31:Q40)</f>
+        <f aca="false">SUM(Q31:Q42)</f>
         <v>0</v>
       </c>
       <c r="R30" s="34" t="n">
-        <f aca="false">SUM(R31:R40)</f>
+        <f aca="false">SUM(R31:R42)</f>
         <v>0</v>
       </c>
       <c r="S30" s="34" t="n">
-        <f aca="false">SUM(S31:S40)</f>
+        <f aca="false">SUM(S31:S42)</f>
         <v>0</v>
       </c>
       <c r="T30" s="34" t="n">
-        <f aca="false">SUM(T31:T40)</f>
+        <f aca="false">SUM(T31:T42)</f>
         <v>0</v>
       </c>
       <c r="U30" s="34" t="n">
-        <f aca="false">SUM(U31:U40)</f>
+        <f aca="false">SUM(U31:U42)</f>
         <v>0</v>
       </c>
       <c r="V30" s="34" t="n">
-        <f aca="false">SUM(V31:V40)</f>
+        <f aca="false">SUM(V31:V42)</f>
         <v>0</v>
       </c>
       <c r="W30" s="34" t="n">
-        <f aca="false">SUM(W31:W40)</f>
+        <f aca="false">SUM(W31:W42)</f>
         <v>0</v>
       </c>
       <c r="X30" s="35" t="s">
@@ -4170,7 +4191,7 @@
       </c>
       <c r="E31" s="32" t="n">
         <f aca="false">SUM(F31:W31)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" s="42"/>
       <c r="G31" s="33"/>
@@ -4180,7 +4201,9 @@
       <c r="I31" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="33"/>
+      <c r="J31" s="33" t="n">
+        <v>2</v>
+      </c>
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
       <c r="M31" s="33"/>
@@ -4195,7 +4218,7 @@
       <c r="V31" s="33"/>
       <c r="W31" s="33"/>
       <c r="X31" s="78" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
@@ -4206,14 +4229,14 @@
       <c r="A32" s="29"/>
       <c r="B32" s="39"/>
       <c r="C32" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D32" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="32" t="n">
         <f aca="false">SUM(F32:W32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="42"/>
       <c r="G32" s="33"/>
@@ -4221,7 +4244,9 @@
       <c r="I32" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="33"/>
+      <c r="J32" s="33" t="n">
+        <v>2</v>
+      </c>
       <c r="K32" s="33"/>
       <c r="L32" s="33"/>
       <c r="M32" s="33"/>
@@ -4236,7 +4261,7 @@
       <c r="V32" s="33"/>
       <c r="W32" s="33"/>
       <c r="X32" s="78" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
@@ -4247,10 +4272,10 @@
       <c r="A33" s="29"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D33" s="41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">SUM(F33:W33)</f>
@@ -4274,9 +4299,7 @@
       <c r="U33" s="33"/>
       <c r="V33" s="33"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="78" t="s">
-        <v>11</v>
-      </c>
+      <c r="X33" s="78"/>
       <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
@@ -4286,10 +4309,10 @@
       <c r="A34" s="29"/>
       <c r="B34" s="39"/>
       <c r="C34" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D34" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="32" t="n">
         <f aca="false">SUM(F34:W34)</f>
@@ -4325,10 +4348,10 @@
       <c r="A35" s="29"/>
       <c r="B35" s="39"/>
       <c r="C35" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D35" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <f aca="false">SUM(F35:W35)</f>
@@ -4364,10 +4387,10 @@
       <c r="A36" s="29"/>
       <c r="B36" s="39"/>
       <c r="C36" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D36" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="32" t="n">
         <f aca="false">SUM(F36:W36)</f>
@@ -4403,10 +4426,10 @@
       <c r="A37" s="29"/>
       <c r="B37" s="39"/>
       <c r="C37" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D37" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="32" t="n">
         <f aca="false">SUM(F37:W37)</f>
@@ -4442,7 +4465,7 @@
       <c r="A38" s="29"/>
       <c r="B38" s="39"/>
       <c r="C38" s="40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D38" s="41" t="n">
         <v>2</v>
@@ -4481,10 +4504,10 @@
       <c r="A39" s="29"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D39" s="41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" s="32" t="n">
         <f aca="false">SUM(F39:W39)</f>
@@ -4508,46 +4531,44 @@
       <c r="U39" s="33"/>
       <c r="V39" s="33"/>
       <c r="W39" s="33"/>
-      <c r="X39" s="78" t="s">
-        <v>11</v>
-      </c>
+      <c r="X39" s="78"/>
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="46"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" s="49" t="n">
+      <c r="A40" s="29"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="50" t="n">
+      <c r="E40" s="32" t="n">
         <f aca="false">SUM(F40:W40)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="51"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="52"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="52"/>
-      <c r="X40" s="54" t="s">
+      <c r="F40" s="42"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="33"/>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="78" t="s">
         <v>11</v>
       </c>
       <c r="Y40" s="6"/>
@@ -4557,91 +4578,36 @@
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="29"/>
-      <c r="B41" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="31" t="n">
-        <f aca="false">SUM(D42:D46)</f>
-        <v>30</v>
+      <c r="B41" s="39"/>
+      <c r="C41" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="E41" s="32" t="n">
         <f aca="false">SUM(F41:W41)</f>
-        <v>7</v>
-      </c>
-      <c r="F41" s="56" t="n">
-        <f aca="false">SUM(F42:F46)</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="34" t="n">
-        <f aca="false">SUM(G42:G46)</f>
-        <v>2</v>
-      </c>
-      <c r="H41" s="34" t="n">
-        <f aca="false">SUM(H42:H46)</f>
-        <v>2</v>
-      </c>
-      <c r="I41" s="34" t="n">
-        <f aca="false">SUM(I42:I46)</f>
-        <v>3</v>
-      </c>
-      <c r="J41" s="34" t="n">
-        <f aca="false">SUM(J42:J46)</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="34" t="n">
-        <f aca="false">SUM(K42:K46)</f>
-        <v>0</v>
-      </c>
-      <c r="L41" s="34" t="n">
-        <f aca="false">SUM(L42:L46)</f>
-        <v>0</v>
-      </c>
-      <c r="M41" s="34" t="n">
-        <f aca="false">SUM(M42:M46)</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="34" t="n">
-        <f aca="false">SUM(N42:N46)</f>
-        <v>0</v>
-      </c>
-      <c r="O41" s="34" t="n">
-        <f aca="false">SUM(O42:O46)</f>
-        <v>0</v>
-      </c>
-      <c r="P41" s="34" t="n">
-        <f aca="false">SUM(P42:P46)</f>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="34" t="n">
-        <f aca="false">SUM(Q42:Q46)</f>
-        <v>0</v>
-      </c>
-      <c r="R41" s="34" t="n">
-        <f aca="false">SUM(R42:R46)</f>
-        <v>0</v>
-      </c>
-      <c r="S41" s="34" t="n">
-        <f aca="false">SUM(S42:S46)</f>
-        <v>0</v>
-      </c>
-      <c r="T41" s="34" t="n">
-        <f aca="false">SUM(T42:T46)</f>
-        <v>0</v>
-      </c>
-      <c r="U41" s="34" t="n">
-        <f aca="false">SUM(U42:U46)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="34" t="n">
-        <f aca="false">SUM(V42:V46)</f>
-        <v>0</v>
-      </c>
-      <c r="W41" s="34" t="n">
-        <f aca="false">SUM(W42:W46)</f>
-        <v>0</v>
-      </c>
-      <c r="X41" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F41" s="42"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="78" t="s">
         <v>11</v>
       </c>
       <c r="Y41" s="6"/>
@@ -4650,39 +4616,37 @@
       <c r="AB41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="29"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="32" t="n">
+      <c r="A42" s="46"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="50" t="n">
         <f aca="false">SUM(F42:W42)</f>
-        <v>2</v>
-      </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F42" s="51"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="54" t="s">
         <v>11</v>
       </c>
       <c r="Y42" s="6"/>
@@ -4692,37 +4656,90 @@
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="29"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="41" t="n">
-        <v>5</v>
+      <c r="B43" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31" t="n">
+        <f aca="false">SUM(D44:D48)</f>
+        <v>30</v>
       </c>
       <c r="E43" s="32" t="n">
         <f aca="false">SUM(F43:W43)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="77"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="43"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="33"/>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
+        <v>9</v>
+      </c>
+      <c r="F43" s="56" t="n">
+        <f aca="false">SUM(F44:F48)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="34" t="n">
+        <f aca="false">SUM(G44:G48)</f>
+        <v>2</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <f aca="false">SUM(H44:H48)</f>
+        <v>2</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <f aca="false">SUM(I44:I48)</f>
+        <v>3</v>
+      </c>
+      <c r="J43" s="34" t="n">
+        <f aca="false">SUM(J44:J48)</f>
+        <v>2</v>
+      </c>
+      <c r="K43" s="34" t="n">
+        <f aca="false">SUM(K44:K48)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="34" t="n">
+        <f aca="false">SUM(L44:L48)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="34" t="n">
+        <f aca="false">SUM(M44:M48)</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="34" t="n">
+        <f aca="false">SUM(N44:N48)</f>
+        <v>0</v>
+      </c>
+      <c r="O43" s="34" t="n">
+        <f aca="false">SUM(O44:O48)</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="34" t="n">
+        <f aca="false">SUM(P44:P48)</f>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="34" t="n">
+        <f aca="false">SUM(Q44:Q48)</f>
+        <v>0</v>
+      </c>
+      <c r="R43" s="34" t="n">
+        <f aca="false">SUM(R44:R48)</f>
+        <v>0</v>
+      </c>
+      <c r="S43" s="34" t="n">
+        <f aca="false">SUM(S44:S48)</f>
+        <v>0</v>
+      </c>
+      <c r="T43" s="34" t="n">
+        <f aca="false">SUM(T44:T48)</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="34" t="n">
+        <f aca="false">SUM(U44:U48)</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="34" t="n">
+        <f aca="false">SUM(V44:V48)</f>
+        <v>0</v>
+      </c>
+      <c r="W43" s="34" t="n">
+        <f aca="false">SUM(W44:W48)</f>
+        <v>0</v>
+      </c>
       <c r="X43" s="35" t="s">
         <v>11</v>
       </c>
@@ -4735,20 +4752,24 @@
       <c r="A44" s="29"/>
       <c r="B44" s="39"/>
       <c r="C44" s="40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D44" s="41" t="n">
         <v>5</v>
       </c>
       <c r="E44" s="32" t="n">
         <f aca="false">SUM(F44:W44)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F44" s="42"/>
       <c r="G44" s="33"/>
       <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
+      <c r="I44" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="33" t="n">
+        <v>2</v>
+      </c>
       <c r="K44" s="33"/>
       <c r="L44" s="33"/>
       <c r="M44" s="77"/>
@@ -4763,7 +4784,7 @@
       <c r="V44" s="33"/>
       <c r="W44" s="33"/>
       <c r="X44" s="35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y44" s="6"/>
       <c r="Z44" s="6"/>
@@ -4774,19 +4795,21 @@
       <c r="A45" s="29"/>
       <c r="B45" s="39"/>
       <c r="C45" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D45" s="41" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="32" t="n">
         <f aca="false">SUM(F45:W45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="42"/>
       <c r="G45" s="33"/>
       <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
+      <c r="I45" s="33" t="n">
+        <v>1</v>
+      </c>
       <c r="J45" s="33"/>
       <c r="K45" s="33"/>
       <c r="L45" s="33"/>
@@ -4802,7 +4825,7 @@
       <c r="V45" s="33"/>
       <c r="W45" s="33"/>
       <c r="X45" s="35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -4810,41 +4833,37 @@
       <c r="AB45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="46"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="D46" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" s="50" t="n">
+      <c r="A46" s="29"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="32" t="n">
         <f aca="false">SUM(F46:W46)</f>
-        <v>4</v>
-      </c>
-      <c r="F46" s="51"/>
-      <c r="G46" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="52"/>
-      <c r="N46" s="79"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="52"/>
-      <c r="Q46" s="52"/>
-      <c r="R46" s="52"/>
-      <c r="S46" s="53"/>
-      <c r="T46" s="52"/>
-      <c r="U46" s="52"/>
-      <c r="V46" s="52"/>
-      <c r="W46" s="52"/>
-      <c r="X46" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="F46" s="42"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="77"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="35" t="s">
         <v>11</v>
       </c>
       <c r="Y46" s="6"/>
@@ -4854,90 +4873,35 @@
     </row>
     <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="29"/>
-      <c r="B47" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="31" t="n">
-        <f aca="false">SUM(D48:D55)</f>
-        <v>32</v>
+      <c r="B47" s="39"/>
+      <c r="C47" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <v>5</v>
       </c>
       <c r="E47" s="32" t="n">
         <f aca="false">SUM(F47:W47)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="56" t="n">
-        <f aca="false">SUM(F48:F55)</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="34" t="n">
-        <f aca="false">SUM(G48:G55)</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="34" t="n">
-        <f aca="false">SUM(H48:H55)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="34" t="n">
-        <f aca="false">SUM(I48:I55)</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="34" t="n">
-        <f aca="false">SUM(J48:J55)</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="34" t="n">
-        <f aca="false">SUM(K48:K55)</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="34" t="n">
-        <f aca="false">SUM(L48:L55)</f>
-        <v>0</v>
-      </c>
-      <c r="M47" s="34" t="n">
-        <f aca="false">SUM(M48:M55)</f>
-        <v>0</v>
-      </c>
-      <c r="N47" s="34" t="n">
-        <f aca="false">SUM(N48:N55)</f>
-        <v>0</v>
-      </c>
-      <c r="O47" s="34" t="n">
-        <f aca="false">SUM(O48:O55)</f>
-        <v>0</v>
-      </c>
-      <c r="P47" s="33" t="n">
-        <f aca="false">SUM(P48:P55)</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="34" t="n">
-        <f aca="false">SUM(Q48:Q55)</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="33" t="n">
-        <f aca="false">SUM(R48:R55)</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="80" t="n">
-        <f aca="false">SUM(S48:S55)</f>
-        <v>0</v>
-      </c>
-      <c r="T47" s="33" t="n">
-        <f aca="false">SUM(T48:T55)</f>
-        <v>0</v>
-      </c>
-      <c r="U47" s="33" t="n">
-        <f aca="false">SUM(U48:U55)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="33" t="n">
-        <f aca="false">SUM(V48:V55)</f>
-        <v>0</v>
-      </c>
-      <c r="W47" s="34" t="n">
-        <f aca="false">SUM(W48:W55)</f>
-        <v>0</v>
-      </c>
+      <c r="F47" s="42"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
       <c r="X47" s="35" t="s">
         <v>11</v>
       </c>
@@ -4947,38 +4911,42 @@
       <c r="AB47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="29"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="41" t="n">
+      <c r="A48" s="46"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="50" t="n">
+        <f aca="false">SUM(F48:W48)</f>
+        <v>4</v>
+      </c>
+      <c r="F48" s="51"/>
+      <c r="G48" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="32" t="n">
-        <f aca="false">SUM(F48:W48)</f>
-        <v>0</v>
-      </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="43"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="35" t="s">
-        <v>11</v>
+      <c r="H48" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="79"/>
+      <c r="O48" s="52"/>
+      <c r="P48" s="52"/>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="52"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="52"/>
+      <c r="U48" s="52"/>
+      <c r="V48" s="52"/>
+      <c r="W48" s="52"/>
+      <c r="X48" s="54" t="s">
+        <v>15</v>
       </c>
       <c r="Y48" s="6"/>
       <c r="Z48" s="6"/>
@@ -4987,35 +4955,90 @@
     </row>
     <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="29"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="41" t="n">
-        <v>5</v>
+      <c r="B49" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="30"/>
+      <c r="D49" s="31" t="n">
+        <f aca="false">SUM(D50:D57)</f>
+        <v>32</v>
       </c>
       <c r="E49" s="32" t="n">
         <f aca="false">SUM(F49:W49)</f>
         <v>0</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="43"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
+      <c r="F49" s="56" t="n">
+        <f aca="false">SUM(F50:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <f aca="false">SUM(G50:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <f aca="false">SUM(H50:H57)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <f aca="false">SUM(I50:I57)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <f aca="false">SUM(J50:J57)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <f aca="false">SUM(K50:K57)</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <f aca="false">SUM(L50:L57)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <f aca="false">SUM(M50:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="34" t="n">
+        <f aca="false">SUM(N50:N57)</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <f aca="false">SUM(O50:O57)</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="33" t="n">
+        <f aca="false">SUM(P50:P57)</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="34" t="n">
+        <f aca="false">SUM(Q50:Q57)</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="33" t="n">
+        <f aca="false">SUM(R50:R57)</f>
+        <v>0</v>
+      </c>
+      <c r="S49" s="80" t="n">
+        <f aca="false">SUM(S50:S57)</f>
+        <v>0</v>
+      </c>
+      <c r="T49" s="33" t="n">
+        <f aca="false">SUM(T50:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U49" s="33" t="n">
+        <f aca="false">SUM(U50:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="33" t="n">
+        <f aca="false">SUM(V50:V57)</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <f aca="false">SUM(W50:W57)</f>
+        <v>0</v>
+      </c>
       <c r="X49" s="35" t="s">
         <v>11</v>
       </c>
@@ -5028,10 +5051,10 @@
       <c r="A50" s="29"/>
       <c r="B50" s="39"/>
       <c r="C50" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D50" s="41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E50" s="32" t="n">
         <f aca="false">SUM(F50:W50)</f>
@@ -5067,10 +5090,10 @@
       <c r="A51" s="29"/>
       <c r="B51" s="39"/>
       <c r="C51" s="40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D51" s="41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" s="32" t="n">
         <f aca="false">SUM(F51:W51)</f>
@@ -5094,7 +5117,9 @@
       <c r="U51" s="33"/>
       <c r="V51" s="33"/>
       <c r="W51" s="33"/>
-      <c r="X51" s="35"/>
+      <c r="X51" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
       <c r="AA51" s="6"/>
@@ -5104,10 +5129,10 @@
       <c r="A52" s="29"/>
       <c r="B52" s="39"/>
       <c r="C52" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D52" s="41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" s="32" t="n">
         <f aca="false">SUM(F52:W52)</f>
@@ -5143,10 +5168,10 @@
       <c r="A53" s="29"/>
       <c r="B53" s="39"/>
       <c r="C53" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D53" s="41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E53" s="32" t="n">
         <f aca="false">SUM(F53:W53)</f>
@@ -5170,9 +5195,7 @@
       <c r="U53" s="33"/>
       <c r="V53" s="33"/>
       <c r="W53" s="33"/>
-      <c r="X53" s="35" t="s">
-        <v>11</v>
-      </c>
+      <c r="X53" s="35"/>
       <c r="Y53" s="6"/>
       <c r="Z53" s="6"/>
       <c r="AA53" s="6"/>
@@ -5182,10 +5205,10 @@
       <c r="A54" s="29"/>
       <c r="B54" s="39"/>
       <c r="C54" s="40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D54" s="41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" s="32" t="n">
         <f aca="false">SUM(F54:W54)</f>
@@ -5221,10 +5244,10 @@
       <c r="A55" s="29"/>
       <c r="B55" s="39"/>
       <c r="C55" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D55" s="41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" s="32" t="n">
         <f aca="false">SUM(F55:W55)</f>
@@ -5257,155 +5280,77 @@
       <c r="AB55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="81"/>
-      <c r="D56" s="82" t="n">
-        <f aca="false">D29+D17+D3</f>
-        <v>239</v>
-      </c>
-      <c r="E56" s="82" t="n">
-        <f aca="false">E29+E17+E3</f>
-        <v>56</v>
-      </c>
-      <c r="F56" s="82" t="n">
-        <f aca="false">F29+F17+F3</f>
-        <v>15</v>
-      </c>
-      <c r="G56" s="82" t="n">
-        <f aca="false">G29+G17+G3</f>
-        <v>12</v>
-      </c>
-      <c r="H56" s="82" t="n">
-        <f aca="false">H29+H17+H3</f>
-        <v>15</v>
-      </c>
-      <c r="I56" s="82" t="n">
-        <f aca="false">I29+I17+I3</f>
-        <v>14</v>
-      </c>
-      <c r="J56" s="82" t="n">
-        <f aca="false">J29+J17+J3</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="82" t="n">
-        <f aca="false">K29+K17+K3</f>
-        <v>0</v>
-      </c>
-      <c r="L56" s="82" t="n">
-        <f aca="false">L29+L17+L3</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="82" t="n">
-        <f aca="false">M29+M17+M3</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="82" t="n">
-        <f aca="false">N29+N17+N3</f>
-        <v>0</v>
-      </c>
-      <c r="O56" s="82" t="n">
-        <f aca="false">O29+O17+O3</f>
-        <v>0</v>
-      </c>
-      <c r="P56" s="82" t="n">
-        <f aca="false">P29+P17+P3</f>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="82" t="n">
-        <f aca="false">Q29+Q17+Q3</f>
-        <v>0</v>
-      </c>
-      <c r="R56" s="82" t="n">
-        <f aca="false">R29+R17+R3</f>
-        <v>0</v>
-      </c>
-      <c r="S56" s="82" t="n">
-        <f aca="false">S29+S17+S3</f>
-        <v>0</v>
-      </c>
-      <c r="T56" s="82" t="n">
-        <f aca="false">T29+T17+T3</f>
-        <v>0</v>
-      </c>
-      <c r="U56" s="82" t="n">
-        <f aca="false">U29+U17+U3</f>
-        <v>0</v>
-      </c>
-      <c r="V56" s="82" t="n">
-        <f aca="false">V29+V17+V3</f>
-        <v>0</v>
-      </c>
-      <c r="W56" s="82"/>
-      <c r="X56" s="83"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="32" t="n">
+        <f aca="false">SUM(F56:W56)</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="42"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="43"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="Y56" s="6"/>
       <c r="Z56" s="6"/>
       <c r="AA56" s="6"/>
       <c r="AB56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="29"/>
+      <c r="B57" s="39"/>
       <c r="C57" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="84" t="n">
-        <f aca="false">SUM(F57:V57)</f>
-        <v>240</v>
-      </c>
-      <c r="E57" s="84" t="n">
-        <f aca="false">SUM(F57:V57)</f>
-        <v>240</v>
-      </c>
-      <c r="F57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="G57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="H57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="I57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="J57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="K57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="L57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="M57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="N57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="O57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="P57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="R57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="S57" s="85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="U57" s="85" t="n">
-        <v>15</v>
-      </c>
-      <c r="V57" s="85" t="n">
-        <v>15</v>
+        <v>78</v>
+      </c>
+      <c r="D57" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="32" t="n">
+        <f aca="false">SUM(F57:W57)</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="42"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
+      <c r="N57" s="33"/>
+      <c r="O57" s="33"/>
+      <c r="P57" s="33"/>
+      <c r="Q57" s="33"/>
+      <c r="R57" s="33"/>
+      <c r="S57" s="43"/>
+      <c r="T57" s="33"/>
+      <c r="U57" s="33"/>
+      <c r="V57" s="33"/>
+      <c r="W57" s="33"/>
+      <c r="X57" s="35" t="s">
+        <v>11</v>
       </c>
       <c r="Y57" s="6"/>
       <c r="Z57" s="6"/>
@@ -5413,92 +5358,246 @@
       <c r="AB57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C58" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="84" t="n">
-        <f aca="false">D57-D56</f>
+      <c r="B58" s="81" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="81"/>
+      <c r="D58" s="82" t="n">
+        <f aca="false">D29+D17+D3</f>
+        <v>248</v>
+      </c>
+      <c r="E58" s="82" t="n">
+        <f aca="false">E29+E17+E3</f>
+        <v>71</v>
+      </c>
+      <c r="F58" s="82" t="n">
+        <f aca="false">F29+F17+F3</f>
+        <v>15</v>
+      </c>
+      <c r="G58" s="82" t="n">
+        <f aca="false">G29+G17+G3</f>
+        <v>12</v>
+      </c>
+      <c r="H58" s="82" t="n">
+        <f aca="false">H29+H17+H3</f>
+        <v>15</v>
+      </c>
+      <c r="I58" s="82" t="n">
+        <f aca="false">I29+I17+I3</f>
+        <v>14</v>
+      </c>
+      <c r="J58" s="82" t="n">
+        <f aca="false">J29+J17+J3</f>
+        <v>15</v>
+      </c>
+      <c r="K58" s="82" t="n">
+        <f aca="false">K29+K17+K3</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="82" t="n">
+        <f aca="false">L29+L17+L3</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="82" t="n">
+        <f aca="false">M29+M17+M3</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="82" t="n">
+        <f aca="false">N29+N17+N3</f>
+        <v>0</v>
+      </c>
+      <c r="O58" s="82" t="n">
+        <f aca="false">O29+O17+O3</f>
+        <v>0</v>
+      </c>
+      <c r="P58" s="82" t="n">
+        <f aca="false">P29+P17+P3</f>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="82" t="n">
+        <f aca="false">Q29+Q17+Q3</f>
+        <v>0</v>
+      </c>
+      <c r="R58" s="82" t="n">
+        <f aca="false">R29+R17+R3</f>
+        <v>0</v>
+      </c>
+      <c r="S58" s="82" t="n">
+        <f aca="false">S29+S17+S3</f>
+        <v>0</v>
+      </c>
+      <c r="T58" s="82" t="n">
+        <f aca="false">T29+T17+T3</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="82" t="n">
+        <f aca="false">U29+U17+U3</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="82" t="n">
+        <f aca="false">V29+V17+V3</f>
+        <v>0</v>
+      </c>
+      <c r="W58" s="82"/>
+      <c r="X58" s="83"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C59" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="84" t="n">
+        <f aca="false">SUM(F59:V59)</f>
+        <v>240</v>
+      </c>
+      <c r="E59" s="84" t="n">
+        <f aca="false">SUM(F59:V59)</f>
+        <v>240</v>
+      </c>
+      <c r="F59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="G59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="I59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="J59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="K59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="L59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="M59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="N59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="O59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="P59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="R59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="S59" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="U59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="V59" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6"/>
+      <c r="AB59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C60" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="84" t="n">
+        <f aca="false">D59-D58</f>
+        <v>-8</v>
+      </c>
+      <c r="E60" s="84" t="n">
+        <f aca="false">E59-E58</f>
+        <v>169</v>
+      </c>
+      <c r="F60" s="84" t="n">
+        <f aca="false">F59-F58</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="84" t="n">
+        <f aca="false">G59-G58</f>
+        <v>3</v>
+      </c>
+      <c r="H60" s="84" t="n">
+        <f aca="false">H59-H58</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="84" t="n">
+        <f aca="false">I59-I58</f>
         <v>1</v>
       </c>
-      <c r="E58" s="84" t="n">
-        <f aca="false">E57-E56</f>
-        <v>184</v>
-      </c>
-      <c r="F58" s="84" t="n">
-        <f aca="false">F57-F56</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="84" t="n">
-        <f aca="false">G57-G56</f>
-        <v>3</v>
-      </c>
-      <c r="H58" s="84" t="n">
-        <f aca="false">H57-H56</f>
-        <v>0</v>
-      </c>
-      <c r="I58" s="84" t="n">
-        <f aca="false">I57-I56</f>
-        <v>1</v>
-      </c>
-      <c r="J58" s="84" t="n">
-        <f aca="false">J57-J56</f>
+      <c r="J60" s="84" t="n">
+        <f aca="false">J59-J58</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="84" t="n">
+        <f aca="false">K59-K58</f>
         <v>15</v>
       </c>
-      <c r="K58" s="84" t="n">
-        <f aca="false">K57-K56</f>
+      <c r="L60" s="84" t="n">
+        <f aca="false">L59-L58</f>
         <v>15</v>
       </c>
-      <c r="L58" s="84" t="n">
-        <f aca="false">L57-L56</f>
+      <c r="M60" s="84" t="n">
+        <f aca="false">M59-M58</f>
         <v>15</v>
       </c>
-      <c r="M58" s="84" t="n">
-        <f aca="false">M57-M56</f>
+      <c r="N60" s="84" t="n">
+        <f aca="false">N59-N58</f>
         <v>15</v>
       </c>
-      <c r="N58" s="84" t="n">
-        <f aca="false">N57-N56</f>
+      <c r="O60" s="84" t="n">
+        <f aca="false">O59-O58</f>
         <v>15</v>
       </c>
-      <c r="O58" s="84" t="n">
-        <f aca="false">O57-O56</f>
+      <c r="P60" s="84" t="n">
+        <f aca="false">P59-P58</f>
         <v>15</v>
       </c>
-      <c r="P58" s="84" t="n">
-        <f aca="false">P57-P56</f>
+      <c r="Q60" s="84" t="n">
+        <f aca="false">Q59-Q58</f>
         <v>15</v>
       </c>
-      <c r="Q58" s="84" t="n">
-        <f aca="false">Q57-Q56</f>
+      <c r="R60" s="84" t="n">
+        <f aca="false">R59-R58</f>
         <v>15</v>
       </c>
-      <c r="R58" s="84" t="n">
-        <f aca="false">R57-R56</f>
+      <c r="S60" s="84" t="n">
+        <f aca="false">S59-S58</f>
+        <v>0</v>
+      </c>
+      <c r="T60" s="84" t="n">
+        <f aca="false">T59-T58</f>
         <v>15</v>
       </c>
-      <c r="S58" s="84" t="n">
-        <f aca="false">S57-S56</f>
-        <v>0</v>
-      </c>
-      <c r="T58" s="84" t="n">
-        <f aca="false">T57-T56</f>
+      <c r="U60" s="84" t="n">
+        <f aca="false">U59-U58</f>
         <v>15</v>
       </c>
-      <c r="U58" s="84" t="n">
-        <f aca="false">U57-U56</f>
+      <c r="V60" s="84" t="n">
+        <f aca="false">V59-V58</f>
         <v>15</v>
       </c>
-      <c r="V58" s="84" t="n">
-        <f aca="false">V57-V56</f>
-        <v>15</v>
-      </c>
-      <c r="Y58" s="86"/>
-      <c r="Z58" s="87"/>
-      <c r="AA58" s="86"/>
-      <c r="AB58" s="86"/>
+      <c r="Y60" s="86"/>
+      <c r="Z60" s="87"/>
+      <c r="AA60" s="86"/>
+      <c r="AB60" s="86"/>
     </row>
-    <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5683,8 +5782,8 @@
     <row r="242" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="243" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="244" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6430,6 +6529,8 @@
     <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A1:C1"/>
@@ -6451,21 +6552,21 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B58:C58"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4 D7 D18 D21 D30 D41">
+  <conditionalFormatting sqref="D4 D7 D18 D21 D30 D43">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D56:W56">
+  <conditionalFormatting sqref="D58:W58">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E10 E18:E22 E30:E46">
+  <conditionalFormatting sqref="E4:E10 E18:E22 E30:E48">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>E4&lt;D4</formula>
     </cfRule>
@@ -6479,12 +6580,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V4:W4 F7:W7 F18:W18 F21:W21 F30:W30 F41:W41 D56:W56">
+  <conditionalFormatting sqref="V4:W4 F7:W7 F18:W18 F21:W21 F30:W30 F43:W43 D58:W58">
     <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X4:X10 X18:X22 X30:X46">
+  <conditionalFormatting sqref="X4:X10 X18:X22 X30:X48">
     <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"Complete"</formula>
     </cfRule>
@@ -6645,12 +6746,12 @@
       <formula>"Very Late &amp; Complete"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47:E55">
+  <conditionalFormatting sqref="E49:E57">
     <cfRule type="expression" priority="56" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="54">
-      <formula>E37&lt;D37</formula>
+      <formula>E38&lt;D38</formula>
     </cfRule>
     <cfRule type="expression" priority="57" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="55">
-      <formula>E37&gt;D37</formula>
+      <formula>E38&gt;D38</formula>
     </cfRule>
     <cfRule type="cellIs" priority="58" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="56">
       <formula>"D5"</formula>
@@ -6659,12 +6760,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47:W47">
+  <conditionalFormatting sqref="F49:W49">
     <cfRule type="cellIs" priority="60" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X47:X55">
+  <conditionalFormatting sqref="X49:X57">
     <cfRule type="cellIs" priority="61" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
       <formula>"Complete"</formula>
     </cfRule>
@@ -6725,7 +6826,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D47">
+  <conditionalFormatting sqref="D49">
     <cfRule type="cellIs" priority="76" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="74">
       <formula>0</formula>
     </cfRule>
@@ -6770,7 +6871,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D58:V58">
+  <conditionalFormatting sqref="D60:V60">
     <cfRule type="cellIs" priority="85" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="83">
       <formula>0</formula>
     </cfRule>
@@ -6833,7 +6934,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7 P18 P21 P30 P41">
+  <conditionalFormatting sqref="P7 P18 P21 P30 P43">
     <cfRule type="cellIs" priority="102" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="100">
       <formula>0</formula>
     </cfRule>
@@ -6853,7 +6954,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P47">
+  <conditionalFormatting sqref="P49">
     <cfRule type="cellIs" priority="106" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="104">
       <formula>0</formula>
     </cfRule>
@@ -6863,7 +6964,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7 S18 S21 S30 S41">
+  <conditionalFormatting sqref="S7 S18 S21 S30 S43">
     <cfRule type="cellIs" priority="108" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="106">
       <formula>0</formula>
     </cfRule>
@@ -6883,7 +6984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S47">
+  <conditionalFormatting sqref="S49">
     <cfRule type="cellIs" priority="112" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="110">
       <formula>0</formula>
     </cfRule>
@@ -6898,7 +6999,7 @@
       <formula1>"Complete,Early &amp; Complete,Ontime (In Progress),Late (In Progress),Very Late &amp; Complete,Very Late (In Progress),Not Started,Late &amp; Completed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X4:X7 X10:X11 X13:X14 X16 X18:X23 X25:X26 X28 X30:X55" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X4:X7 X10:X11 X13:X14 X16 X18:X23 X25:X26 X28 X30:X57" type="list">
       <formula1>"Complete,Early &amp; Complete,Ontime (In Progress),Late (In Progress),Very Late &amp; Complete,Very Late (In Progress),Not Started,Late &amp; Complete"</formula1>
       <formula2>0</formula2>
     </dataValidation>
